--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/nov-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2508.26</v>
+        <v>2487.02</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1057.17</v>
+        <v>1048.21</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3858.08</v>
+        <v>3825.41</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1603.08</v>
+        <v>1589.51</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>30204.74</v>
+        <v>29948.92</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>853.91</v>
+        <v>846.6799999999999</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>846.4299999999999</v>
+        <v>839.26</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8416.719999999999</v>
+        <v>8345.43</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>39311.56</v>
+        <v>38978.62</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>515.9</v>
+        <v>511.53</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23523.45</v>
+        <v>23324.22</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7253.71</v>
+        <v>7192.27</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1423.94</v>
+        <v>1411.88</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>812.23</v>
+        <v>805.35</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>14873.93</v>
+        <v>14747.96</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>22630.71</v>
+        <v>22439.04</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>913.76</v>
+        <v>909.0599999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5472.39</v>
+        <v>5444.27</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>21811.88</v>
+        <v>21699.81</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>20.31</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12290.31</v>
+        <v>12227.16</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5792.08</v>
+        <v>5762.32</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4274.89</v>
+        <v>4252.92</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>692</v>
+        <v>688.45</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11727.72</v>
+        <v>11667.46</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>390.27</v>
+        <v>388.27</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>30458.56</v>
+        <v>30302.06</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>374.05</v>
+        <v>372.13</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9665.52</v>
+        <v>9615.85</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11477.8</v>
+        <v>11418.83</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>18350.98</v>
+        <v>18256.69</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>26718.04</v>
+        <v>26580.76</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12824.66</v>
+        <v>12758.76</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9166.110000000001</v>
+        <v>9119.01</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>545.05</v>
+        <v>542.25</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1068.72</v>
+        <v>1063.23</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1817.12</v>
+        <v>1807.78</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3906.08</v>
+        <v>3886.01</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>14000.25</v>
+        <v>13928.32</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>21374.43</v>
+        <v>21264.61</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>480.92</v>
+        <v>478.45</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>304.59</v>
+        <v>301.55</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3758.11</v>
+        <v>3720.6</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>36595.96</v>
+        <v>36230.73</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13306.74</v>
+        <v>13173.93</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>584.8</v>
+        <v>578.97</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5477.46</v>
+        <v>5422.8</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>710.7</v>
+        <v>703.61</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>16752.21</v>
+        <v>16585.02</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>718.8200000000001</v>
+        <v>711.65</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>609.17</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>609.17</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>609.17</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>10305.15</v>
+        <v>10202.3</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>355.35</v>
+        <v>351.8</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>62089.78</v>
+        <v>61470.12</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6162.23</v>
+        <v>6100.73</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>39507.8</v>
+        <v>39113.51</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>57238.77</v>
+        <v>56667.52</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1068.72</v>
+        <v>1058.06</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>14782.56</v>
+        <v>14635.02</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>70535.62</v>
+        <v>69831.66</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2670.1</v>
+        <v>2643.45</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>76199.84</v>
+        <v>75439.36</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4274.89</v>
+        <v>4232.22</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1212.03</v>
+        <v>1199.93</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5343.61</v>
+        <v>5290.28</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3051.89</v>
+        <v>3021.44</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>820.35</v>
+        <v>812.16</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>23235.46</v>
+        <v>23003.57</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4274.89</v>
+        <v>4232.22</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>41829.76</v>
+        <v>41391.71</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>24522.29</v>
+        <v>24265.49</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>21669.98</v>
+        <v>21443.05</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8548.299999999999</v>
+        <v>8458.780000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1567.09</v>
+        <v>1550.68</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5375.97</v>
+        <v>5319.67</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>12396.63</v>
+        <v>12266.81</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>203.06</v>
+        <v>200.93</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4365.73</v>
+        <v>4320.01</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>27412.71</v>
+        <v>27125.63</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>19168.59</v>
+        <v>18967.85</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>10558.97</v>
+        <v>10448.39</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>335.04</v>
+        <v>331.54</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>8076.6</v>
+        <v>7992.02</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>894.47</v>
+        <v>885.1</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>192.9</v>
+        <v>190.88</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1981.63</v>
+        <v>1960.88</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>47109.24</v>
+        <v>46615.91</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2137.44</v>
+        <v>2115.06</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2606.24</v>
+        <v>2578.94</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>138.93</v>
+        <v>137.48</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>22643.91</v>
+        <v>22406.78</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>213.74</v>
+        <v>211.51</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>53.44</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>20305.71</v>
+        <v>20093.06</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>944.1900000000001</v>
+        <v>934.3099999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>429.47</v>
+        <v>424.97</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4078.24</v>
+        <v>4055.95</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>21096.62</v>
+        <v>20981.3</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>285.35</v>
+        <v>283.79</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>300.31</v>
+        <v>298.67</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2137.44</v>
+        <v>2125.76</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>82301.88</v>
+        <v>81852.03</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>12625.88</v>
+        <v>12556.86</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5087.97</v>
+        <v>5060.16</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>39922.24</v>
+        <v>39704.03</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1435.61</v>
+        <v>1427.77</v>
       </c>
     </row>
     <row r="110">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>12680.38</v>
+        <v>12611.07</v>
       </c>
     </row>
     <row r="111">
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>11755.94</v>
+        <v>11691.68</v>
       </c>
     </row>
     <row r="112">
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1298.5</v>
+        <v>1291.4</v>
       </c>
     </row>
     <row r="113">
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>797</v>
+        <v>792.64</v>
       </c>
     </row>
     <row r="114">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>8228.73</v>
+        <v>8183.75</v>
       </c>
     </row>
     <row r="115">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>63996.54</v>
+        <v>63646.74</v>
       </c>
     </row>
     <row r="116">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4381.76</v>
+        <v>4357.81</v>
       </c>
     </row>
     <row r="117">
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>352.68</v>
+        <v>350.75</v>
       </c>
     </row>
     <row r="118">
@@ -7641,7 +7641,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4768.21</v>
+        <v>4742.15</v>
       </c>
     </row>
     <row r="119">
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1816.75</v>
+        <v>1806.82</v>
       </c>
     </row>
     <row r="120">
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3848.21</v>
+        <v>3827.18</v>
       </c>
     </row>
     <row r="121">
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>50061.16</v>
+        <v>49503.41</v>
       </c>
     </row>
     <row r="122">
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>527.95</v>
+        <v>522.0700000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>137.32</v>
+        <v>135.79</v>
       </c>
     </row>
     <row r="124">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>145.69</v>
+        <v>144.07</v>
       </c>
     </row>
     <row r="125">
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>355.35</v>
+        <v>351.39</v>
       </c>
     </row>
     <row r="126">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>253.82</v>
+        <v>250.99</v>
       </c>
     </row>
     <row r="127">
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>22460.14</v>
+        <v>22209.9</v>
       </c>
     </row>
     <row r="128">
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>27595.46</v>
+        <v>27288</v>
       </c>
     </row>
     <row r="129">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>19475.51</v>
+        <v>19258.52</v>
       </c>
     </row>
     <row r="130">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>640.34</v>
+        <v>633.21</v>
       </c>
     </row>
     <row r="131">
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>64447.83</v>
+        <v>63729.79</v>
       </c>
     </row>
     <row r="132">
@@ -8491,7 +8491,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>15828.3</v>
+        <v>15651.95</v>
       </c>
     </row>
     <row r="133">
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>10855.43</v>
+        <v>10734.49</v>
       </c>
     </row>
     <row r="134">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5339.24</v>
+        <v>5279.76</v>
       </c>
     </row>
     <row r="135">
@@ -8674,7 +8674,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8632.1</v>
+        <v>8535.93</v>
       </c>
     </row>
     <row r="136">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>31365.72</v>
+        <v>31016.26</v>
       </c>
     </row>
     <row r="137">
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>66263.16</v>
+        <v>65524.89</v>
       </c>
     </row>
     <row r="138">
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>21320.99</v>
+        <v>21083.45</v>
       </c>
     </row>
     <row r="139">
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>13542.84</v>
+        <v>13391.95</v>
       </c>
     </row>
     <row r="140">
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>28188.6</v>
+        <v>28034.22</v>
       </c>
     </row>
     <row r="141">
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>23351.56</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="142">
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1739.79</v>
+        <v>1730.27</v>
       </c>
     </row>
     <row r="143">
@@ -9162,7 +9162,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4213.33</v>
+        <v>4190.25</v>
       </c>
     </row>
     <row r="144">
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>18122.84</v>
+        <v>18023.6</v>
       </c>
     </row>
     <row r="145">
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3385.71</v>
+        <v>3367.17</v>
       </c>
     </row>
     <row r="146">
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>990</v>
+        <v>984.58</v>
       </c>
     </row>
     <row r="147">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>60917.12</v>
+        <v>60583.51</v>
       </c>
     </row>
     <row r="148">
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1068.72</v>
+        <v>1062.87</v>
       </c>
     </row>
     <row r="149">
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4937.49</v>
+        <v>4910.45</v>
       </c>
     </row>
     <row r="150">
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>15122.67</v>
+        <v>15039.86</v>
       </c>
     </row>
     <row r="151">
@@ -9650,7 +9650,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>11929.82</v>
+        <v>11864.48</v>
       </c>
     </row>
     <row r="152">
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1988.58</v>
+        <v>1977.69</v>
       </c>
     </row>
     <row r="153">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2150.58</v>
+        <v>2138.8</v>
       </c>
     </row>
     <row r="154">
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1631.06</v>
+        <v>1622.12</v>
       </c>
     </row>
     <row r="155">
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>459.42</v>
+        <v>456.9</v>
       </c>
     </row>
     <row r="156">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>20696.59</v>
+        <v>20583.25</v>
       </c>
     </row>
     <row r="157">
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>213.74</v>
+        <v>212.57</v>
       </c>
     </row>
     <row r="158">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>25671.76</v>
+        <v>25531.17</v>
       </c>
     </row>
     <row r="159">
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>673.5700000000001</v>
+        <v>672.71</v>
       </c>
     </row>
     <row r="160">
@@ -10199,7 +10199,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>8368.09</v>
+        <v>8357.440000000001</v>
       </c>
     </row>
     <row r="161">
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1599.43</v>
+        <v>1597.39</v>
       </c>
     </row>
     <row r="162">
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>76146.39999999999</v>
+        <v>76049.48</v>
       </c>
     </row>
     <row r="163">
@@ -10382,7 +10382,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>28510.75</v>
+        <v>28474.46</v>
       </c>
     </row>
     <row r="164">
@@ -10443,7 +10443,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2821.42</v>
+        <v>2817.83</v>
       </c>
     </row>
     <row r="165">
@@ -10504,7 +10504,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>9448.25</v>
+        <v>9436.219999999999</v>
       </c>
     </row>
     <row r="166">
@@ -10565,7 +10565,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>534.36</v>
+        <v>533.6799999999999</v>
       </c>
     </row>
     <row r="167">
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>13604.82</v>
+        <v>13587.51</v>
       </c>
     </row>
     <row r="168">
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>9061.42</v>
+        <v>9049.889999999999</v>
       </c>
     </row>
     <row r="169">
@@ -10748,7 +10748,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>57972.8</v>
+        <v>57899.01</v>
       </c>
     </row>
     <row r="170">
@@ -10809,7 +10809,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>22816.51</v>
+        <v>22787.47</v>
       </c>
     </row>
     <row r="171">
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>28652.27</v>
+        <v>28615.8</v>
       </c>
     </row>
     <row r="172">
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>22443.15</v>
+        <v>22414.59</v>
       </c>
     </row>
     <row r="173">
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>69039.41</v>
+        <v>68951.53</v>
       </c>
     </row>
     <row r="174">
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>8155.28</v>
+        <v>8144.9</v>
       </c>
     </row>
     <row r="175">
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2137.43</v>
+        <v>2134.71</v>
       </c>
     </row>
     <row r="176">
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>4274.89</v>
+        <v>4269.45</v>
       </c>
     </row>
     <row r="177">
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>873.65</v>
+        <v>872.54</v>
       </c>
     </row>
     <row r="178">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>16691.29</v>
+        <v>16750.86</v>
       </c>
     </row>
     <row r="179">
@@ -11362,7 +11362,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1615.91</v>
+        <v>1621.67</v>
       </c>
     </row>
     <row r="180">
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>40466.74</v>
+        <v>40611.16</v>
       </c>
     </row>
     <row r="181">
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>9917.309999999999</v>
+        <v>9952.700000000001</v>
       </c>
     </row>
     <row r="182">
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>12371.25</v>
+        <v>12415.4</v>
       </c>
     </row>
     <row r="183">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>36920.85</v>
+        <v>37052.62</v>
       </c>
     </row>
     <row r="184">
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>13300.24</v>
+        <v>13347.7</v>
       </c>
     </row>
     <row r="185">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>324.89</v>
+        <v>326.05</v>
       </c>
     </row>
     <row r="186">
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>854.98</v>
+        <v>858.03</v>
       </c>
     </row>
     <row r="187">
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>243.67</v>
+        <v>244.54</v>
       </c>
     </row>
     <row r="188">
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>467.03</v>
+        <v>468.7</v>
       </c>
     </row>
     <row r="189">
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>19405.66</v>
+        <v>19474.91</v>
       </c>
     </row>
     <row r="190">
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>7279.6</v>
+        <v>7305.58</v>
       </c>
     </row>
     <row r="191">
@@ -12094,7 +12094,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>25220.7</v>
+        <v>25310.71</v>
       </c>
     </row>
     <row r="192">
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2056.56</v>
+        <v>2063.9</v>
       </c>
     </row>
     <row r="193">
@@ -12216,7 +12216,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>6350.61</v>
+        <v>6373.28</v>
       </c>
     </row>
     <row r="194">
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1167.11</v>
+        <v>1171.28</v>
       </c>
     </row>
     <row r="195">
@@ -12338,7 +12338,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3056.54</v>
+        <v>3067.45</v>
       </c>
     </row>
     <row r="196">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>35160.94</v>
+        <v>35286.42</v>
       </c>
     </row>
     <row r="197">
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>14293.19</v>
+        <v>14344.2</v>
       </c>
     </row>
     <row r="198">
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>659.9299999999999</v>
+        <v>667.11</v>
       </c>
     </row>
     <row r="199">
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>641.23</v>
+        <v>648.21</v>
       </c>
     </row>
     <row r="200">
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>25008.08</v>
+        <v>25280.08</v>
       </c>
     </row>
     <row r="201">
@@ -12704,7 +12704,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1045.97</v>
+        <v>1057.35</v>
       </c>
     </row>
     <row r="202">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>60917.12</v>
+        <v>61579.68</v>
       </c>
     </row>
     <row r="203">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2233.63</v>
+        <v>2257.92</v>
       </c>
     </row>
     <row r="204">
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2297.75</v>
+        <v>2322.74</v>
       </c>
     </row>
     <row r="205">
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>152.29</v>
+        <v>153.95</v>
       </c>
     </row>
     <row r="206">
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>314.74</v>
+        <v>318.16</v>
       </c>
     </row>
     <row r="207">
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>162.45</v>
+        <v>164.21</v>
       </c>
     </row>
     <row r="208">
@@ -13131,7 +13131,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>304.59</v>
+        <v>307.9</v>
       </c>
     </row>
     <row r="209">
@@ -13192,7 +13192,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>355.35</v>
+        <v>359.22</v>
       </c>
     </row>
     <row r="210">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>220.32</v>
+        <v>222.71</v>
       </c>
     </row>
     <row r="211">
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>23794.01</v>
+        <v>24052.81</v>
       </c>
     </row>
     <row r="212">
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1483.56</v>
+        <v>1499.69</v>
       </c>
     </row>
     <row r="213">
@@ -13436,7 +13436,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>139.08</v>
+        <v>140.6</v>
       </c>
     </row>
     <row r="214">
@@ -13497,7 +13497,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1746.27</v>
+        <v>1765.26</v>
       </c>
     </row>
     <row r="215">
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>293.62</v>
+        <v>296.81</v>
       </c>
     </row>
     <row r="216">
@@ -13619,7 +13619,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1401.14</v>
+        <v>1416.38</v>
       </c>
     </row>
     <row r="217">
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>6282.59</v>
+        <v>6350.92</v>
       </c>
     </row>
     <row r="218">
@@ -13741,7 +13741,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>122.26</v>
+        <v>122.66</v>
       </c>
     </row>
     <row r="219">
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>801.54</v>
+        <v>804.1799999999999</v>
       </c>
     </row>
     <row r="220">
@@ -13863,7 +13863,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3622.97</v>
+        <v>3634.88</v>
       </c>
     </row>
     <row r="221">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>14705.61</v>
+        <v>14753.97</v>
       </c>
     </row>
     <row r="222">
@@ -13985,7 +13985,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>10687.22</v>
+        <v>10722.37</v>
       </c>
     </row>
     <row r="223">
@@ -14046,7 +14046,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>507.64</v>
+        <v>509.31</v>
       </c>
     </row>
     <row r="224">
@@ -14107,7 +14107,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>101.53</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="225">
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>304.59</v>
+        <v>305.59</v>
       </c>
     </row>
     <row r="226">
@@ -14229,7 +14229,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>101.53</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="227">
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>50.76</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="228">
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>304.59</v>
+        <v>305.59</v>
       </c>
     </row>
     <row r="229">
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7751.7</v>
+        <v>7777.2</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>89066.03999999999</v>
+        <v>89358.98</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3473.34</v>
+        <v>3484.77</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>20305.71</v>
+        <v>20656.22</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2910.18</v>
+        <v>2960.42</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>10007.51</v>
+        <v>10180.25</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>8801.66</v>
+        <v>8953.59</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>15069.02</v>
+        <v>15329.14</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>253.82</v>
+        <v>258.2</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>15186.53</v>
+        <v>15448.68</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>10687.22</v>
+        <v>10871.69</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>563.77</v>
+        <v>573.5</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>28.86</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2921.02</v>
+        <v>2971.44</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>19286.07</v>
+        <v>19618.97</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>128.25</v>
+        <v>130.46</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>470.24</v>
+        <v>478.35</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1025.97</v>
+        <v>1043.68</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>726.73</v>
+        <v>739.27</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>111.68</v>
+        <v>113.61</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1731.86</v>
+        <v>1761.76</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>11909.68</v>
+        <v>12115.26</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>470.24</v>
+        <v>478.35</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1449.83</v>
+        <v>1474.85</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2726.29</v>
+        <v>2773.35</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>40725.63</v>
+        <v>41428.62</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>205.37</v>
+        <v>208.92</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3740.52</v>
+        <v>3766.44</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>24521.9</v>
+        <v>24691.78</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>18918.44</v>
+        <v>19049.5</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>21234.57</v>
+        <v>21381.67</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>168.32</v>
+        <v>169.49</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>46870.47</v>
+        <v>47195.17</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>5437.55</v>
+        <v>5475.22</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>302.02</v>
+        <v>304.11</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>752.38</v>
+        <v>755.88</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>341.99</v>
+        <v>343.58</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2244.07</v>
+        <v>2254.52</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>13371.31</v>
+        <v>13433.58</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>32061.64</v>
+        <v>32210.96</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>4761.69</v>
+        <v>4783.87</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>21302.72</v>
+        <v>21401.93</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>56.41</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>12004.74</v>
+        <v>12060.64</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>26524.21</v>
+        <v>26647.74</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>47154.93</v>
+        <v>47374.54</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>470.24</v>
+        <v>472.43</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>12345.87</v>
+        <v>12434.88</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>21374.43</v>
+        <v>21528.53</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>28410.08</v>
+        <v>28614.9</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>21070.98</v>
+        <v>21222.88</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>9676.200000000001</v>
+        <v>9745.959999999999</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1833.93</v>
+        <v>1847.15</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>13490.26</v>
+        <v>13587.51</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>5355.63</v>
+        <v>5394.24</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>3206.16</v>
+        <v>3229.28</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>4514.28</v>
+        <v>4546.82</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>20002.61</v>
+        <v>20146.82</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>22443.15</v>
+        <v>22604.95</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>3527.1</v>
+        <v>3552.53</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>11295.57</v>
+        <v>11275.54</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1068.72</v>
+        <v>1066.83</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>11182.86</v>
+        <v>11163.03</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>406.11</v>
+        <v>405.39</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>427.49</v>
+        <v>426.73</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3648.96</v>
+        <v>3642.49</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>213.74</v>
+        <v>213.37</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>4083.09</v>
+        <v>4075.85</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>37405.25</v>
+        <v>37338.91</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1705.68</v>
+        <v>1702.65</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>10687.22</v>
+        <v>10668.26</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>8794.91</v>
+        <v>8779.309999999999</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>8382.200000000001</v>
+        <v>8367.33</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>708.1</v>
+        <v>706.85</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>20305.71</v>
+        <v>20222.02</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>21320.99</v>
+        <v>21233.12</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>40467.25</v>
+        <v>40300.46</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1715.63</v>
+        <v>1708.56</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>3309.83</v>
+        <v>3296.19</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>13894.18</v>
+        <v>13836.91</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>15229.28</v>
+        <v>15166.51</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>609.17</v>
+        <v>606.66</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>10993.51</v>
+        <v>10948.2</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>30.46</v>
+        <v>30.33</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>25788.25</v>
+        <v>25681.96</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>18523.94</v>
+        <v>18447.59</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>17145.61</v>
+        <v>17074.94</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>25613.62</v>
+        <v>25508.05</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2975.29</v>
+        <v>2963.03</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>424.9</v>
+        <v>423.15</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>80538.85000000001</v>
+        <v>80206.89999999999</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>5087.69</v>
+        <v>5066.72</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>609.17</v>
+        <v>606.66</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>52449.64</v>
+        <v>52233.47</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>18614.19</v>
+        <v>18537.48</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1627.66</v>
+        <v>1620.95</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2642.68</v>
+        <v>2631.79</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>7919.23</v>
+        <v>7886.59</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>558.74</v>
+        <v>556.4400000000001</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>26611.95</v>
+        <v>26570.7</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>12837.48</v>
+        <v>12817.59</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>261.75</v>
+        <v>261.35</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>726.4400000000001</v>
+        <v>725.3099999999999</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5571.06</v>
+        <v>5562.43</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>11126.37</v>
+        <v>11109.13</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>9529.26</v>
+        <v>9514.49</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>6861.19</v>
+        <v>6850.56</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>6412.33</v>
+        <v>6402.39</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>564.28</v>
+        <v>563.41</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>7863.38</v>
+        <v>7851.2</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>495.36</v>
+        <v>494.59</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2885.55</v>
+        <v>2881.08</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1184.03</v>
+        <v>1182.19</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>171.17</v>
+        <v>170.9</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>267.18</v>
+        <v>266.77</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>55840.7</v>
+        <v>55754.15</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>30966.2</v>
+        <v>30918.21</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>34509.71</v>
+        <v>34456.23</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>22272.32</v>
+        <v>22237.8</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>3505.41</v>
+        <v>3499.97</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>15982.93</v>
+        <v>15958.16</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>639.63</v>
+        <v>638.64</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2013.47</v>
+        <v>2023.87</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1603.08</v>
+        <v>1611.36</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>9061.42</v>
+        <v>9108.219999999999</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1852.39</v>
+        <v>1861.96</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>1015.29</v>
+        <v>1020.53</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>5033.68</v>
+        <v>5059.67</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>4230.78</v>
+        <v>4252.63</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>4274.89</v>
+        <v>4296.96</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>5418.42</v>
+        <v>5446.4</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>6946.69</v>
+        <v>6982.56</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1816.82</v>
+        <v>1826.21</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>152.29</v>
+        <v>153.08</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>36650.28</v>
+        <v>36839.56</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>47999.86</v>
+        <v>48247.75</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>805.39</v>
+        <v>809.55</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>7249.14</v>
+        <v>7286.58</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>48275.35</v>
+        <v>48524.66</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>545.05</v>
+        <v>547.86</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1707559.25</v>
+        <v>1716377.79</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>752.38</v>
+        <v>756.27</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>12824.66</v>
+        <v>12890.89</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>4138.09</v>
+        <v>4159.46</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1295.5</v>
+        <v>1302.19</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>224.43</v>
+        <v>225.59</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>9404.75</v>
+        <v>9453.32</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>5247.68</v>
+        <v>5274.79</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>6589.2</v>
+        <v>6623.23</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>3745.6</v>
+        <v>3764.95</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>9535.51</v>
+        <v>9584.75</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>43764.14</v>
+        <v>43990.16</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>893.45</v>
+        <v>898.0700000000001</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>336.65</v>
+        <v>338.39</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>17840.09</v>
+        <v>17932.22</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>9503.07</v>
+        <v>9552.15</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>8600.99</v>
+        <v>8645.41</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2671.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>56451.91</v>
+        <v>56850.33</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>8062.38</v>
+        <v>8119.28</v>
       </c>
     </row>
     <row r="390">
@@ -24233,7 +24233,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>683.98</v>
+        <v>688.8099999999999</v>
       </c>
     </row>
     <row r="391">
@@ -24294,7 +24294,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>752.38</v>
+        <v>757.6900000000001</v>
       </c>
     </row>
     <row r="392">
@@ -24355,7 +24355,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>32846.63</v>
+        <v>33078.45</v>
       </c>
     </row>
     <row r="393">
@@ -24416,7 +24416,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>24876.02</v>
+        <v>25051.58</v>
       </c>
     </row>
     <row r="394">
@@ -24477,7 +24477,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>2137.44</v>
+        <v>2152.53</v>
       </c>
     </row>
     <row r="395">
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>9084.129999999999</v>
+        <v>9148.24</v>
       </c>
     </row>
     <row r="396">
@@ -24599,7 +24599,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1588.85</v>
+        <v>1600.06</v>
       </c>
     </row>
     <row r="397">
@@ -24660,7 +24660,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>33657.68</v>
+        <v>33895.22</v>
       </c>
     </row>
     <row r="398">
@@ -24721,7 +24721,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>961.85</v>
+        <v>968.64</v>
       </c>
     </row>
     <row r="399">
@@ -24782,7 +24782,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1128.57</v>
+        <v>1136.53</v>
       </c>
     </row>
     <row r="400">
@@ -24843,7 +24843,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>25476.97</v>
+        <v>25656.77</v>
       </c>
     </row>
     <row r="401">
@@ -24904,7 +24904,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>99.56</v>
+        <v>100.26</v>
       </c>
     </row>
     <row r="402">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>39961.63</v>
+        <v>40243.67</v>
       </c>
     </row>
     <row r="403">
@@ -25026,7 +25026,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>21384.96</v>
+        <v>21535.88</v>
       </c>
     </row>
     <row r="404">
@@ -25087,7 +25087,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2662.02</v>
+        <v>2680.8</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>75500.89</v>
+        <v>76033.74000000001</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>6113.09</v>
+        <v>6156.23</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>4832.76</v>
+        <v>4866.87</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>63054.81</v>
+        <v>63499.82</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>10329.11</v>
+        <v>10402.01</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>24732.35</v>
+        <v>24906.9</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>149621.1</v>
+        <v>150677.07</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/nov-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -24945,7 +24945,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/nov-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/nov-2025.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION V REGIÓN</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO CONTROL FINANCIERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asociación de Municipios Metropolitanos </t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIRECCION DE INFANCIA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7130,7 +7130,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -7189,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7311,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7372,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7433,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7560,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7677,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7736,7 +7740,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -8227,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8344,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Departamento Provincial San Felipe-Los Andes</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8405,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8527,7 +8535,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8588,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8832,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8893,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9076,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Gendarmería de Ch</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9198,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9442,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9747,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9808,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9869,7 +9877,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9930,7 +9938,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10174,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10479,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10540,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10723,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10784,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11093,7 +11101,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11154,7 +11162,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11215,7 +11223,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11276,7 +11284,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11398,7 +11406,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11459,7 +11467,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11825,7 +11833,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11886,7 +11894,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11947,7 +11955,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12069,7 +12077,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12191,7 +12199,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12252,7 +12260,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12313,7 +12321,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12374,7 +12382,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Defensoría Penal Pública</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12435,7 +12443,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12557,7 +12565,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12862,7 +12870,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13899,7 +13907,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13960,7 +13968,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14574,7 +14582,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14635,7 +14643,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14696,7 +14704,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15184,7 +15192,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15367,7 +15375,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15428,7 +15436,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15489,7 +15497,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15550,7 +15558,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15611,7 +15619,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15855,7 +15863,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15977,7 +15985,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16038,7 +16046,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16099,7 +16107,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16526,7 +16534,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17319,7 +17327,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17751,7 +17759,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17807,12 +17815,12 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ÑUBLE DEL SERVICIO DE REGISTRO CIVIL E IDENTIFIC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -18173,7 +18181,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18295,7 +18303,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18600,7 +18608,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18722,7 +18730,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18783,7 +18791,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Unidad Contable Disalcar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19027,7 +19035,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19149,7 +19157,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19515,7 +19523,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19759,7 +19767,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19820,7 +19828,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20003,7 +20011,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20125,7 +20133,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20369,7 +20377,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20552,7 +20560,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Dirección Servicio Metropolitano Oriente</t>
+          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20674,7 +20682,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20979,7 +20987,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21101,7 +21109,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21223,7 +21231,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIO</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21345,7 +21353,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales VII Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21406,7 +21414,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales VII Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21528,7 +21536,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21711,7 +21719,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21777,7 +21785,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21833,7 +21841,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -22077,7 +22085,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22321,7 +22329,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22504,7 +22512,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -22936,7 +22944,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23541,7 +23549,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -23602,7 +23610,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA Va ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -23663,7 +23671,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -23846,7 +23854,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -23907,7 +23915,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -23968,7 +23976,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO FRONTERAS OS3</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24151,7 +24159,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24210,7 +24218,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H390" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -24396,7 +24408,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24452,7 +24464,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24513,7 +24525,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24574,7 +24586,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -24696,7 +24708,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -24818,7 +24830,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -24879,7 +24891,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -25062,7 +25074,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25188,7 +25200,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25249,7 +25261,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -25310,7 +25322,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -25432,7 +25444,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -25493,7 +25505,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/nov-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/nov-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14539,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14600,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14661,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14722,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14783,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14844,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14905,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14966,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15027,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15088,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15210,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15271,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15332,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15393,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15454,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15515,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15576,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15637,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15698,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15759,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15820,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15881,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15942,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16003,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16064,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16125,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16186,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16247,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16308,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16369,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16430,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16491,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16613,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16674,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16918,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17040,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17162,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17223,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17284,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +18437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17467,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17528,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17772,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17833,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17894,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18016,7 +19152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18077,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18138,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18199,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18260,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18321,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18382,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18443,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18504,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18565,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18626,7 +19802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18687,7 +19867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18748,7 +19932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18809,7 +19997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18870,7 +20062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18931,7 +20127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18992,7 +20192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19053,7 +20257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19114,7 +20322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19175,7 +20387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19236,7 +20452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19297,7 +20517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19358,7 +20582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19419,7 +20647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19480,7 +20712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19541,7 +20777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19602,7 +20842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19663,7 +20907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19724,7 +20972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19785,7 +21037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19846,7 +21102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19907,7 +21167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19968,7 +21232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +21297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20090,7 +21362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20151,7 +21427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20212,7 +21492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20273,7 +21557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20334,7 +21622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20395,7 +21687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20456,7 +21752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20517,7 +21817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20578,7 +21882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20639,7 +21947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20700,7 +22012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20761,7 +22077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20822,7 +22142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20883,7 +22207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20944,7 +22272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21005,7 +22337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21066,7 +22402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21127,7 +22467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21188,7 +22532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21249,7 +22597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21310,7 +22662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21371,7 +22727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +22792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21493,7 +22857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21554,7 +22922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21615,7 +22987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21676,7 +23052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21737,7 +23117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21798,7 +23182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21859,7 +23247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21920,7 +23312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21981,7 +23377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22042,7 +23442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +23507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22164,7 +23572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22225,7 +23637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22286,7 +23702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22347,7 +23767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22408,7 +23832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22469,7 +23897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22530,7 +23962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +24027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22652,7 +24092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22713,7 +24157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22774,7 +24222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22835,7 +24287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22896,7 +24352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22957,7 +24417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23018,7 +24482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23079,7 +24547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23140,7 +24612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23201,7 +24677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23262,7 +24742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23323,7 +24807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23384,7 +24872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23445,7 +24937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23506,7 +25002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23567,7 +25067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23628,7 +25132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23689,7 +25197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23750,7 +25262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23811,7 +25327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23872,7 +25392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23933,7 +25457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23994,7 +25522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24055,7 +25587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24116,7 +25652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24177,7 +25717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24238,7 +25782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24299,7 +25847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24360,7 +25912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24421,7 +25977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24482,7 +26042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24543,7 +26107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24604,7 +26172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24665,7 +26237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24726,7 +26302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24787,7 +26367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24848,7 +26432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +26497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24970,7 +26562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25031,7 +26627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25092,7 +26692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25218,7 +26822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25279,7 +26887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25340,7 +26952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25401,7 +27017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25462,7 +27082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25523,7 +27147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
